--- a/5. Knife/output/yearly_population_growth_param_0.5.xlsx
+++ b/5. Knife/output/yearly_population_growth_param_0.5.xlsx
@@ -775,13 +775,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>85217</v>
+        <v>84632</v>
       </c>
       <c r="C2" t="n">
-        <v>235</v>
+        <v>464</v>
       </c>
       <c r="D2" t="n">
-        <v>32936</v>
+        <v>63837</v>
       </c>
     </row>
     <row r="3">
@@ -789,13 +789,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>48829</v>
+        <v>48332</v>
       </c>
       <c r="C3" t="n">
-        <v>304</v>
+        <v>515</v>
       </c>
       <c r="D3" t="n">
-        <v>12729</v>
+        <v>21742</v>
       </c>
     </row>
     <row r="4">
@@ -803,13 +803,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28067</v>
+        <v>27789</v>
       </c>
       <c r="C4" t="n">
-        <v>482</v>
+        <v>724</v>
       </c>
       <c r="D4" t="n">
-        <v>4983</v>
+        <v>6689</v>
       </c>
     </row>
     <row r="5">
@@ -817,13 +817,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16298</v>
+        <v>16576</v>
       </c>
       <c r="C5" t="n">
-        <v>504</v>
+        <v>707</v>
       </c>
       <c r="D5" t="n">
-        <v>1793</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="6">
@@ -831,13 +831,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9462</v>
+        <v>9808</v>
       </c>
       <c r="C6" t="n">
-        <v>348</v>
+        <v>484</v>
       </c>
       <c r="D6" t="n">
-        <v>798</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7">
@@ -845,13 +845,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6101</v>
+        <v>6243</v>
       </c>
       <c r="C7" t="n">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8">
@@ -859,13 +859,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4565</v>
+        <v>4835</v>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -873,13 +873,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2173</v>
+        <v>2700</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>343</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -887,13 +887,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>470</v>
+        <v>685</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -901,13 +901,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
@@ -918,10 +918,10 @@
         <v>110</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
@@ -929,13 +929,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -943,13 +943,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">
@@ -957,13 +957,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -971,13 +971,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -985,13 +985,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -999,13 +999,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -1013,13 +1013,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -1027,13 +1027,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -1041,13 +1041,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1086,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>92832</v>
       </c>
       <c r="C2" t="n">
-        <v>210</v>
+        <v>433</v>
       </c>
       <c r="D2" t="n">
-        <v>27184</v>
+        <v>52960</v>
       </c>
     </row>
     <row r="3">
@@ -1100,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>56366</v>
+        <v>54176</v>
       </c>
       <c r="C3" t="n">
-        <v>268</v>
+        <v>466</v>
       </c>
       <c r="D3" t="n">
-        <v>13331</v>
+        <v>22986</v>
       </c>
     </row>
     <row r="4">
@@ -1114,13 +1114,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34005</v>
+        <v>32726</v>
       </c>
       <c r="C4" t="n">
-        <v>430</v>
+        <v>655</v>
       </c>
       <c r="D4" t="n">
-        <v>5277</v>
+        <v>7433</v>
       </c>
     </row>
     <row r="5">
@@ -1128,13 +1128,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20088</v>
+        <v>19551</v>
       </c>
       <c r="C5" t="n">
-        <v>488</v>
+        <v>689</v>
       </c>
       <c r="D5" t="n">
-        <v>1891</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="6">
@@ -1142,13 +1142,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11998</v>
+        <v>12057</v>
       </c>
       <c r="C6" t="n">
-        <v>376</v>
+        <v>521</v>
       </c>
       <c r="D6" t="n">
-        <v>835</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -1156,13 +1156,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7223</v>
+        <v>7300</v>
       </c>
       <c r="C7" t="n">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="D7" t="n">
-        <v>487</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -1170,13 +1170,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4911</v>
+        <v>5045</v>
       </c>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -1184,13 +1184,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2837</v>
+        <v>3333</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -1198,13 +1198,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>896</v>
+        <v>1353</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1212,13 +1212,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>209</v>
+        <v>308</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12">
@@ -1226,13 +1226,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -1240,13 +1240,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -1254,13 +1254,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15">
@@ -1268,13 +1268,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16">
@@ -1282,13 +1282,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -1296,13 +1296,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -1310,13 +1310,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -1324,13 +1324,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -1338,13 +1338,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -1352,13 +1352,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1397,13 +1397,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>102972</v>
+        <v>95864</v>
       </c>
       <c r="C2" t="n">
-        <v>153</v>
+        <v>330</v>
       </c>
       <c r="D2" t="n">
-        <v>31261</v>
+        <v>62157</v>
       </c>
     </row>
     <row r="3">
@@ -1411,13 +1411,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>62339</v>
+        <v>57963</v>
       </c>
       <c r="C3" t="n">
-        <v>240</v>
+        <v>428</v>
       </c>
       <c r="D3" t="n">
-        <v>13334</v>
+        <v>23284</v>
       </c>
     </row>
     <row r="4">
@@ -1425,13 +1425,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38605</v>
+        <v>36115</v>
       </c>
       <c r="C4" t="n">
-        <v>388</v>
+        <v>594</v>
       </c>
       <c r="D4" t="n">
-        <v>5631</v>
+        <v>8031</v>
       </c>
     </row>
     <row r="5">
@@ -1439,13 +1439,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23780</v>
+        <v>22172</v>
       </c>
       <c r="C5" t="n">
-        <v>467</v>
+        <v>661</v>
       </c>
       <c r="D5" t="n">
-        <v>1963</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="6">
@@ -1453,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14444</v>
+        <v>14064</v>
       </c>
       <c r="C6" t="n">
-        <v>392</v>
+        <v>542</v>
       </c>
       <c r="D6" t="n">
-        <v>869</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="7">
@@ -1467,13 +1467,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8485</v>
+        <v>8506</v>
       </c>
       <c r="C7" t="n">
-        <v>229</v>
+        <v>313</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -1481,13 +1481,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5381</v>
+        <v>5437</v>
       </c>
       <c r="C8" t="n">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -1495,13 +1495,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3269</v>
+        <v>3679</v>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -1509,13 +1509,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1263</v>
+        <v>1848</v>
       </c>
       <c r="C10" t="n">
         <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1523,13 +1523,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>310</v>
+        <v>589</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
@@ -1537,13 +1537,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
@@ -1551,13 +1551,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>134</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -1565,13 +1565,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -1593,13 +1593,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -1607,13 +1607,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -1621,13 +1621,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -1635,13 +1635,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1649,13 +1649,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -1663,13 +1663,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1708,13 +1708,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>103370</v>
+        <v>92949</v>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>279</v>
       </c>
       <c r="D2" t="n">
-        <v>27429</v>
+        <v>54942</v>
       </c>
     </row>
     <row r="3">
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>65642</v>
+        <v>59214</v>
       </c>
       <c r="C3" t="n">
-        <v>212</v>
+        <v>385</v>
       </c>
       <c r="D3" t="n">
-        <v>13411</v>
+        <v>23721</v>
       </c>
     </row>
     <row r="4">
@@ -1736,13 +1736,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41966</v>
+        <v>38086</v>
       </c>
       <c r="C4" t="n">
-        <v>354</v>
+        <v>548</v>
       </c>
       <c r="D4" t="n">
-        <v>5883</v>
+        <v>8441</v>
       </c>
     </row>
     <row r="5">
@@ -1750,13 +1750,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26891</v>
+        <v>24188</v>
       </c>
       <c r="C5" t="n">
-        <v>445</v>
+        <v>630</v>
       </c>
       <c r="D5" t="n">
-        <v>2008</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="6">
@@ -1764,13 +1764,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16593</v>
+        <v>15597</v>
       </c>
       <c r="C6" t="n">
-        <v>400</v>
+        <v>546</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="7">
@@ -1778,13 +1778,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9805</v>
+        <v>9660</v>
       </c>
       <c r="C7" t="n">
-        <v>248</v>
+        <v>343</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
@@ -1792,13 +1792,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5916</v>
+        <v>5924</v>
       </c>
       <c r="C8" t="n">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -1806,13 +1806,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3600</v>
+        <v>3904</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -1820,13 +1820,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1528</v>
+        <v>2215</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1834,13 +1834,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>418</v>
+        <v>852</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1848,13 +1848,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>130</v>
+        <v>244</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13">
@@ -1862,13 +1862,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
@@ -1876,13 +1876,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
@@ -1890,13 +1890,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -1904,13 +1904,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -1918,13 +1918,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18">
@@ -1932,13 +1932,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -1946,13 +1946,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -1960,13 +1960,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -1974,13 +1974,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2019,13 +2019,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>103471</v>
+        <v>91681</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="D2" t="n">
-        <v>29622</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="3">
@@ -2033,13 +2033,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>66123</v>
+        <v>58605</v>
       </c>
       <c r="C3" t="n">
-        <v>187</v>
+        <v>347</v>
       </c>
       <c r="D3" t="n">
-        <v>13456</v>
+        <v>23831</v>
       </c>
     </row>
     <row r="4">
@@ -2047,13 +2047,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43887</v>
+        <v>38354</v>
       </c>
       <c r="C4" t="n">
-        <v>324</v>
+        <v>507</v>
       </c>
       <c r="D4" t="n">
-        <v>5993</v>
+        <v>8917</v>
       </c>
     </row>
     <row r="5">
@@ -2061,13 +2061,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29083</v>
+        <v>25603</v>
       </c>
       <c r="C5" t="n">
-        <v>423</v>
+        <v>593</v>
       </c>
       <c r="D5" t="n">
-        <v>2077</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="6">
@@ -2075,13 +2075,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18704</v>
+        <v>16857</v>
       </c>
       <c r="C6" t="n">
-        <v>404</v>
+        <v>550</v>
       </c>
       <c r="D6" t="n">
-        <v>904</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="7">
@@ -2089,13 +2089,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10899</v>
+        <v>10551</v>
       </c>
       <c r="C7" t="n">
-        <v>262</v>
+        <v>365</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -2103,13 +2103,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6475</v>
+        <v>6515</v>
       </c>
       <c r="C8" t="n">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2117,13 +2117,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3877</v>
+        <v>4109</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -2131,13 +2131,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1717</v>
+        <v>2441</v>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2145,13 +2145,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>497</v>
+        <v>1084</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -2159,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
+        <v>351</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
@@ -2173,13 +2173,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14">
@@ -2187,13 +2187,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>86</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -2201,13 +2201,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16">
@@ -2215,13 +2215,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -2229,13 +2229,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -2243,13 +2243,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -2257,13 +2257,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -2271,13 +2271,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -2285,13 +2285,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2330,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>87637</v>
+        <v>79102</v>
       </c>
       <c r="C2" t="n">
-        <v>92</v>
+        <v>209</v>
       </c>
       <c r="D2" t="n">
-        <v>24731</v>
+        <v>50230</v>
       </c>
     </row>
     <row r="3">
@@ -2344,13 +2344,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>76508</v>
+        <v>66332</v>
       </c>
       <c r="C3" t="n">
-        <v>288</v>
+        <v>496</v>
       </c>
       <c r="D3" t="n">
-        <v>13322</v>
+        <v>23102</v>
       </c>
     </row>
     <row r="4">
@@ -2358,13 +2358,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39585</v>
+        <v>34440</v>
       </c>
       <c r="C4" t="n">
-        <v>534</v>
+        <v>769</v>
       </c>
       <c r="D4" t="n">
-        <v>5311</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="5">
@@ -2372,13 +2372,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17282</v>
+        <v>15575</v>
       </c>
       <c r="C5" t="n">
-        <v>456</v>
+        <v>635</v>
       </c>
       <c r="D5" t="n">
-        <v>1758</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="6">
@@ -2386,13 +2386,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10070</v>
+        <v>9749</v>
       </c>
       <c r="C6" t="n">
-        <v>256</v>
+        <v>357</v>
       </c>
       <c r="D6" t="n">
-        <v>597</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7">
@@ -2400,13 +2400,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5982</v>
+        <v>6019</v>
       </c>
       <c r="C7" t="n">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="D7" t="n">
-        <v>376</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8">
@@ -2414,13 +2414,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3582</v>
+        <v>3796</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
-        <v>315</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9">
@@ -2428,13 +2428,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1586</v>
+        <v>2255</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2442,13 +2442,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>459</v>
+        <v>1001</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2456,13 +2456,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>128</v>
+        <v>324</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -2470,13 +2470,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -2484,13 +2484,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -2498,13 +2498,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -2512,13 +2512,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -2526,13 +2526,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -2540,13 +2540,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -2554,13 +2554,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -2568,13 +2568,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -2582,13 +2582,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2641,13 +2641,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18599</v>
+        <v>19972</v>
       </c>
       <c r="C2" t="n">
-        <v>2013</v>
+        <v>3017</v>
       </c>
       <c r="D2" t="n">
-        <v>8103</v>
+        <v>11698</v>
       </c>
     </row>
     <row r="3">
@@ -2655,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" t="n">
-        <v>3674</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="4">
@@ -2669,13 +2669,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C4" t="n">
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>2595</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="5">
@@ -2683,13 +2683,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" t="n">
-        <v>672</v>
+        <v>701</v>
       </c>
     </row>
     <row r="6">
@@ -2697,13 +2697,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7">
@@ -2711,13 +2711,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8">
@@ -2725,13 +2725,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2745,7 +2745,7 @@
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -2753,13 +2753,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" t="n">
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -2767,13 +2767,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
@@ -2781,13 +2781,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
@@ -2795,13 +2795,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -2823,13 +2823,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -2837,13 +2837,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2851,13 +2851,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -2865,13 +2865,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -2882,10 +2882,10 @@
         <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -2896,10 +2896,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -2907,10 +2907,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2952,13 +2952,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12208</v>
+        <v>13215</v>
       </c>
       <c r="C2" t="n">
-        <v>1083</v>
+        <v>1637</v>
       </c>
       <c r="D2" t="n">
-        <v>17597</v>
+        <v>28415</v>
       </c>
     </row>
     <row r="3">
@@ -2966,13 +2966,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14881</v>
+        <v>15818</v>
       </c>
       <c r="C3" t="n">
-        <v>786</v>
+        <v>1153</v>
       </c>
       <c r="D3" t="n">
-        <v>3911</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="4">
@@ -2980,10 +2980,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n">
         <v>2675</v>
@@ -2994,13 +2994,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C5" t="n">
         <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>861</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6">
@@ -3008,13 +3008,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C6" t="n">
         <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7">
@@ -3022,13 +3022,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8">
@@ -3036,13 +3036,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -3050,13 +3050,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C9" t="n">
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -3070,7 +3070,7 @@
         <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -3084,7 +3084,7 @@
         <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -3092,13 +3092,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -3106,13 +3106,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -3126,7 +3126,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -3134,13 +3134,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -3148,13 +3148,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -3162,13 +3162,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -3176,13 +3176,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -3193,10 +3193,10 @@
         <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -3204,13 +3204,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -3218,13 +3218,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3263,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2959</v>
+        <v>5453</v>
       </c>
       <c r="C2" t="n">
-        <v>854</v>
+        <v>1300</v>
       </c>
       <c r="D2" t="n">
-        <v>17575</v>
+        <v>29183</v>
       </c>
     </row>
     <row r="3">
@@ -3277,13 +3277,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9951</v>
+        <v>10688</v>
       </c>
       <c r="C3" t="n">
-        <v>812</v>
+        <v>1198</v>
       </c>
       <c r="D3" t="n">
-        <v>5134</v>
+        <v>6549</v>
       </c>
     </row>
     <row r="4">
@@ -3291,13 +3291,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12307</v>
+        <v>12944</v>
       </c>
       <c r="C4" t="n">
-        <v>384</v>
+        <v>547</v>
       </c>
       <c r="D4" t="n">
-        <v>2736</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="5">
@@ -3305,13 +3305,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C5" t="n">
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>1034</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6">
@@ -3319,13 +3319,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" t="n">
-        <v>515</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7">
@@ -3333,13 +3333,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C7" t="n">
         <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8">
@@ -3347,13 +3347,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -3364,10 +3364,10 @@
         <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -3375,13 +3375,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C10" t="n">
         <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -3395,7 +3395,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
@@ -3403,13 +3403,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
@@ -3417,13 +3417,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -3431,13 +3431,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -3445,13 +3445,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -3459,13 +3459,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -3473,13 +3473,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -3490,10 +3490,10 @@
         <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -3501,13 +3501,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -3515,13 +3515,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -3529,13 +3529,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22147</v>
+        <v>24992</v>
       </c>
       <c r="C2" t="n">
-        <v>709</v>
+        <v>1133</v>
       </c>
       <c r="D2" t="n">
-        <v>27307</v>
+        <v>47669</v>
       </c>
     </row>
     <row r="3">
@@ -3588,13 +3588,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2842</v>
+        <v>4741</v>
       </c>
       <c r="C3" t="n">
-        <v>744</v>
+        <v>1102</v>
       </c>
       <c r="D3" t="n">
-        <v>6165</v>
+        <v>8504</v>
       </c>
     </row>
     <row r="4">
@@ -3602,13 +3602,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9143</v>
+        <v>9590</v>
       </c>
       <c r="C4" t="n">
-        <v>556</v>
+        <v>804</v>
       </c>
       <c r="D4" t="n">
-        <v>2955</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="5">
@@ -3616,13 +3616,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9247</v>
+        <v>9830</v>
       </c>
       <c r="C5" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="D5" t="n">
-        <v>1165</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
@@ -3630,13 +3630,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
-        <v>558</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7">
@@ -3644,13 +3644,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8">
@@ -3658,13 +3658,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -3672,13 +3672,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -3686,13 +3686,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -3700,13 +3700,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C11" t="n">
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
@@ -3714,13 +3714,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -3728,13 +3728,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -3742,13 +3742,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -3759,10 +3759,10 @@
         <v>37</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -3770,13 +3770,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -3784,13 +3784,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -3801,10 +3801,10 @@
         <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -3812,13 +3812,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -3826,13 +3826,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -3840,13 +3840,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3885,13 +3885,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27874</v>
+        <v>32779</v>
       </c>
       <c r="C2" t="n">
-        <v>518</v>
+        <v>858</v>
       </c>
       <c r="D2" t="n">
-        <v>25821</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="3">
@@ -3899,13 +3899,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16212</v>
+        <v>17919</v>
       </c>
       <c r="C3" t="n">
-        <v>659</v>
+        <v>997</v>
       </c>
       <c r="D3" t="n">
-        <v>7888</v>
+        <v>11760</v>
       </c>
     </row>
     <row r="4">
@@ -3913,13 +3913,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3401</v>
+        <v>4821</v>
       </c>
       <c r="C4" t="n">
-        <v>623</v>
+        <v>893</v>
       </c>
       <c r="D4" t="n">
-        <v>3204</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="5">
@@ -3927,13 +3927,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8337</v>
+        <v>8589</v>
       </c>
       <c r="C5" t="n">
-        <v>324</v>
+        <v>458</v>
       </c>
       <c r="D5" t="n">
-        <v>1312</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="6">
@@ -3941,13 +3941,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6785</v>
+        <v>7383</v>
       </c>
       <c r="C6" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D6" t="n">
-        <v>603</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7">
@@ -3955,13 +3955,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8">
@@ -3969,13 +3969,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -3983,13 +3983,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>341</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -3997,13 +3997,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -4011,13 +4011,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4025,13 +4025,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
@@ -4039,13 +4039,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -4053,13 +4053,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -4067,13 +4067,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -4081,13 +4081,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -4095,13 +4095,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -4109,13 +4109,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -4123,13 +4123,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -4137,13 +4137,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -4151,13 +4151,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4196,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40954</v>
+        <v>44084</v>
       </c>
       <c r="C2" t="n">
-        <v>385</v>
+        <v>669</v>
       </c>
       <c r="D2" t="n">
-        <v>29166</v>
+        <v>53372</v>
       </c>
     </row>
     <row r="3">
@@ -4210,13 +4210,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21164</v>
+        <v>24141</v>
       </c>
       <c r="C3" t="n">
-        <v>553</v>
+        <v>856</v>
       </c>
       <c r="D3" t="n">
-        <v>9011</v>
+        <v>14090</v>
       </c>
     </row>
     <row r="4">
@@ -4224,13 +4224,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12211</v>
+        <v>13269</v>
       </c>
       <c r="C4" t="n">
-        <v>623</v>
+        <v>902</v>
       </c>
       <c r="D4" t="n">
-        <v>3631</v>
+        <v>4357</v>
       </c>
     </row>
     <row r="5">
@@ -4238,13 +4238,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4292</v>
+        <v>5187</v>
       </c>
       <c r="C5" t="n">
-        <v>423</v>
+        <v>594</v>
       </c>
       <c r="D5" t="n">
-        <v>1435</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="6">
@@ -4252,13 +4252,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7644</v>
+        <v>7862</v>
       </c>
       <c r="C6" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="D6" t="n">
-        <v>656</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7">
@@ -4266,10 +4266,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4382</v>
+        <v>4953</v>
       </c>
       <c r="C7" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D7" t="n">
         <v>443</v>
@@ -4280,13 +4280,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -4294,13 +4294,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>342</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -4308,13 +4308,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -4322,13 +4322,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12">
@@ -4339,10 +4339,10 @@
         <v>91</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -4350,13 +4350,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -4364,13 +4364,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -4378,13 +4378,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -4392,13 +4392,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
@@ -4406,13 +4406,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -4420,13 +4420,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -4434,13 +4434,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -4448,13 +4448,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -4462,13 +4462,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4507,13 +4507,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54183</v>
+        <v>57270</v>
       </c>
       <c r="C2" t="n">
-        <v>295</v>
+        <v>531</v>
       </c>
       <c r="D2" t="n">
-        <v>36624</v>
+        <v>69425</v>
       </c>
     </row>
     <row r="3">
@@ -4521,13 +4521,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29702</v>
+        <v>31298</v>
       </c>
       <c r="C3" t="n">
-        <v>455</v>
+        <v>724</v>
       </c>
       <c r="D3" t="n">
-        <v>10352</v>
+        <v>16443</v>
       </c>
     </row>
     <row r="4">
@@ -4535,13 +4535,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16693</v>
+        <v>18406</v>
       </c>
       <c r="C4" t="n">
-        <v>586</v>
+        <v>859</v>
       </c>
       <c r="D4" t="n">
-        <v>4071</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="5">
@@ -4549,13 +4549,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8863</v>
+        <v>9447</v>
       </c>
       <c r="C5" t="n">
-        <v>481</v>
+        <v>679</v>
       </c>
       <c r="D5" t="n">
-        <v>1560</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="6">
@@ -4563,13 +4563,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5310</v>
+        <v>5801</v>
       </c>
       <c r="C6" t="n">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>707</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -4577,13 +4577,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6150</v>
+        <v>6461</v>
       </c>
       <c r="C7" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="D7" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8">
@@ -4591,13 +4591,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2430</v>
+        <v>2895</v>
       </c>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -4605,13 +4605,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>346</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -4619,13 +4619,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -4633,13 +4633,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12">
@@ -4647,13 +4647,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
@@ -4661,13 +4661,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -4675,13 +4675,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -4689,13 +4689,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -4703,13 +4703,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
@@ -4717,13 +4717,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -4731,13 +4731,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -4745,13 +4745,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -4759,13 +4759,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -4773,13 +4773,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4818,13 +4818,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>72865</v>
+        <v>75156</v>
       </c>
       <c r="C2" t="n">
-        <v>205</v>
+        <v>384</v>
       </c>
       <c r="D2" t="n">
-        <v>37708</v>
+        <v>72524</v>
       </c>
     </row>
     <row r="3">
@@ -4832,13 +4832,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38187</v>
+        <v>39113</v>
       </c>
       <c r="C3" t="n">
-        <v>372</v>
+        <v>613</v>
       </c>
       <c r="D3" t="n">
-        <v>11680</v>
+        <v>19363</v>
       </c>
     </row>
     <row r="4">
@@ -4846,13 +4846,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22439</v>
+        <v>23291</v>
       </c>
       <c r="C4" t="n">
-        <v>539</v>
+        <v>794</v>
       </c>
       <c r="D4" t="n">
-        <v>4529</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="5">
@@ -4860,13 +4860,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12438</v>
+        <v>13214</v>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
+        <v>708</v>
       </c>
       <c r="D5" t="n">
-        <v>1681</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="6">
@@ -4874,13 +4874,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7154</v>
+        <v>7488</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>426</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7">
@@ -4888,13 +4888,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5532</v>
+        <v>5795</v>
       </c>
       <c r="C7" t="n">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="D7" t="n">
-        <v>462</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -4902,13 +4902,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4110</v>
+        <v>4540</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -4916,13 +4916,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1135</v>
+        <v>1490</v>
       </c>
       <c r="C9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>345</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -4930,13 +4930,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -4944,13 +4944,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12">
@@ -4958,13 +4958,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
@@ -4972,13 +4972,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>147</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -4986,13 +4986,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5000,13 +5000,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5014,13 +5014,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
@@ -5028,13 +5028,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5042,13 +5042,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -5056,13 +5056,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>19</v>
+      </c>
+      <c r="C19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5070,13 +5070,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -5084,13 +5084,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
